--- a/outputs/52233.xlsx
+++ b/outputs/52233.xlsx
@@ -386,7 +386,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="2" t="n">
-        <f aca="false">SUM(INDEX($B$3:$Z$5,0,MATCH(A7,$B$2:$Z$2,0)))</f>
+        <f aca="false">SUM(INDEX($3:$5,0,MATCH(A7,$2:$2,0)))</f>
         <v>1000</v>
       </c>
     </row>
@@ -395,7 +395,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="n">
-        <f aca="false">SUM(INDEX($B$3:$Z$5,0,MATCH(A8,$B$2:$Z$2,0)))</f>
+        <f aca="false">SUM(INDEX($3:$5,0,MATCH(A8,$2:$2,0)))</f>
         <v>700</v>
       </c>
     </row>
@@ -404,7 +404,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="n">
-        <f aca="false">SUM(INDEX($B$3:$Z$5,0,MATCH(A9,$B$2:$Z$2,0)))</f>
+        <f aca="false">SUM(INDEX($3:$5,0,MATCH(A9,$2:$2,0)))</f>
         <v>1400</v>
       </c>
     </row>
@@ -413,7 +413,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="n">
-        <f aca="false">SUM(INDEX($B$3:$Z$5,0,MATCH(A10,$B$2:$Z$2,0)))</f>
+        <f aca="false">SUM(INDEX($3:$5,0,MATCH(A10,$2:$2,0)))</f>
         <v>1550</v>
       </c>
     </row>
